--- a/JsonConverter/ExcelFiles/Wave.xlsx
+++ b/JsonConverter/ExcelFiles/Wave.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFE480F-6095-4154-894E-2ABA908EDD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FCDE99-B3AF-4E89-A5ED-13838C553A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -55,10 +55,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>대기 시간</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Id</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -188,6 +184,10 @@
   </si>
   <si>
     <t>enemy_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 시작 이후 언제 소환하는지 시간</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -715,7 +715,8 @@
     <col min="3" max="3" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.5703125" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="44.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="40" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="12.5703125" style="2"/>
@@ -723,7 +724,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -738,7 +739,7 @@
         <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -771,22 +772,22 @@
     </row>
     <row r="3" spans="1:14" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="F3" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>13</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
@@ -795,13 +796,13 @@
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="13">
         <v>1</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="14">
         <v>3</v>
@@ -823,13 +824,13 @@
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="16">
         <v>1</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="14">
         <v>3</v>
@@ -851,13 +852,13 @@
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="14">
         <v>2</v>
@@ -879,13 +880,13 @@
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="17">
         <v>1</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="18">
         <v>5</v>
@@ -907,13 +908,13 @@
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1">
       <c r="A8" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="18">
         <v>5</v>
@@ -935,13 +936,13 @@
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1">
       <c r="A9" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="18">
         <v>3</v>
@@ -963,13 +964,13 @@
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="20">
         <v>1</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="21">
         <v>8</v>
@@ -991,13 +992,13 @@
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="22">
         <v>1</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" s="21">
         <v>3</v>
@@ -1019,13 +1020,13 @@
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="22">
         <v>2</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="21">
         <v>5</v>
@@ -1047,13 +1048,13 @@
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1">
       <c r="A13" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" s="23">
         <v>1</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="24">
         <v>5</v>
@@ -1075,13 +1076,13 @@
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1">
       <c r="A14" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="25">
         <v>1</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" s="24">
         <v>5</v>
@@ -1103,13 +1104,13 @@
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1">
       <c r="A15" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="25">
         <v>2</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" s="24">
         <v>3</v>
@@ -1131,13 +1132,13 @@
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1">
       <c r="A16" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="24">
         <v>2</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" s="24">
         <v>3</v>
@@ -1155,13 +1156,13 @@
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1">
       <c r="A17" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="24">
         <v>3</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D17" s="24">
         <v>2</v>
@@ -1179,13 +1180,13 @@
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="26">
         <v>1</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="27">
         <v>5</v>
@@ -1203,13 +1204,13 @@
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1">
       <c r="A19" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="28">
         <v>1</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" s="27">
         <v>5</v>
@@ -1227,13 +1228,13 @@
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="28">
         <v>1</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" s="27">
         <v>3</v>
@@ -1251,13 +1252,13 @@
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="28">
         <v>2</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" s="27">
         <v>3</v>
@@ -1275,13 +1276,13 @@
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="28">
         <v>2</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" s="27">
         <v>2</v>
@@ -1299,13 +1300,13 @@
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="27">
         <v>3</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" s="27">
         <v>2</v>
@@ -1323,13 +1324,13 @@
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="28">
         <v>3</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" s="27">
         <v>2</v>
@@ -1347,13 +1348,13 @@
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="28">
         <v>4</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D25" s="27">
         <v>1</v>

--- a/JsonConverter/ExcelFiles/Wave.xlsx
+++ b/JsonConverter/ExcelFiles/Wave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FCDE99-B3AF-4E89-A5ED-13838C553A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7CFC76-9591-4202-91B3-18B233F5F546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7050" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -79,14 +79,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>enemy_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemy_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>wave1_03</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -175,19 +167,27 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>enemy_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemy_04</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>enemy_05</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>게임 시작 이후 언제 소환하는지 시간</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_05</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -724,7 +724,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -739,7 +739,7 @@
         <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -796,13 +796,13 @@
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" s="13">
         <v>1</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D4" s="14">
         <v>3</v>
@@ -824,13 +824,13 @@
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" s="16">
         <v>1</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D5" s="14">
         <v>3</v>
@@ -852,13 +852,13 @@
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D6" s="14">
         <v>2</v>
@@ -880,13 +880,13 @@
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="17">
         <v>1</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D7" s="18">
         <v>5</v>
@@ -908,13 +908,13 @@
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1">
       <c r="A8" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D8" s="18">
         <v>5</v>
@@ -936,13 +936,13 @@
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1">
       <c r="A9" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="18">
         <v>3</v>
@@ -964,13 +964,13 @@
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" s="20">
         <v>1</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D10" s="21">
         <v>8</v>
@@ -992,13 +992,13 @@
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" s="22">
         <v>1</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="21">
         <v>3</v>
@@ -1020,13 +1020,13 @@
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" s="22">
         <v>2</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="21">
         <v>5</v>
@@ -1048,13 +1048,13 @@
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1">
       <c r="A13" s="23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B13" s="23">
         <v>1</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D13" s="24">
         <v>5</v>
@@ -1076,13 +1076,13 @@
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1">
       <c r="A14" s="23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" s="25">
         <v>1</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D14" s="24">
         <v>5</v>
@@ -1104,13 +1104,13 @@
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1">
       <c r="A15" s="23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15" s="25">
         <v>2</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D15" s="24">
         <v>3</v>
@@ -1132,13 +1132,13 @@
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1">
       <c r="A16" s="23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B16" s="24">
         <v>2</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D16" s="24">
         <v>3</v>
@@ -1156,13 +1156,13 @@
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1">
       <c r="A17" s="23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B17" s="24">
         <v>3</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D17" s="24">
         <v>2</v>
@@ -1180,13 +1180,13 @@
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" s="26">
         <v>1</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D18" s="27">
         <v>5</v>
@@ -1204,13 +1204,13 @@
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1">
       <c r="A19" s="26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B19" s="28">
         <v>1</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D19" s="27">
         <v>5</v>
@@ -1228,13 +1228,13 @@
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B20" s="28">
         <v>1</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D20" s="27">
         <v>3</v>
@@ -1252,13 +1252,13 @@
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B21" s="28">
         <v>2</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D21" s="27">
         <v>3</v>
@@ -1276,13 +1276,13 @@
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B22" s="28">
         <v>2</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D22" s="27">
         <v>2</v>
@@ -1300,13 +1300,13 @@
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B23" s="27">
         <v>3</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D23" s="27">
         <v>2</v>
@@ -1324,13 +1324,13 @@
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B24" s="28">
         <v>3</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D24" s="27">
         <v>2</v>
@@ -1348,13 +1348,13 @@
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B25" s="28">
         <v>4</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D25" s="27">
         <v>1</v>

--- a/JsonConverter/ExcelFiles/Wave.xlsx
+++ b/JsonConverter/ExcelFiles/Wave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7CFC76-9591-4202-91B3-18B233F5F546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0A9A76-F9E1-4A0A-8194-E04AB48B5753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7050" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="2700" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -79,94 +79,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>wave1_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave1_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave1_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave2_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave2_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave2_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>wave 고유 ID</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>wave3_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave3_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave3_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave4_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave4_02</t>
-  </si>
-  <si>
-    <t>wave5_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave5_02</t>
-  </si>
-  <si>
-    <t>wave5_03</t>
-  </si>
-  <si>
-    <t>wave4_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave4_04</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave4_05</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave5_04</t>
-  </si>
-  <si>
-    <t>wave5_06</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave5_05</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave5_07</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wave5_08</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>게임 시작 이후 언제 소환하는지 시간</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -188,6 +104,94 @@
   </si>
   <si>
     <t>Enemy_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave1_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave1_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave1_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave4_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave4_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave4_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave4_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave4_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave5_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave5_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave5_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave5_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave5_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave5_06</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave5_07</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave5_08</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -724,7 +728,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -739,7 +743,7 @@
         <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -796,13 +800,13 @@
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B4" s="13">
         <v>1</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D4" s="14">
         <v>3</v>
@@ -824,13 +828,13 @@
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
       <c r="A5" s="13" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B5" s="16">
         <v>1</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D5" s="14">
         <v>3</v>
@@ -852,13 +856,13 @@
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D6" s="14">
         <v>2</v>
@@ -880,13 +884,13 @@
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B7" s="17">
         <v>1</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D7" s="18">
         <v>5</v>
@@ -908,13 +912,13 @@
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1">
       <c r="A8" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B8" s="19">
         <v>1</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D8" s="18">
         <v>5</v>
@@ -936,13 +940,13 @@
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1">
       <c r="A9" s="17" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B9" s="19">
         <v>1</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D9" s="18">
         <v>3</v>
@@ -964,13 +968,13 @@
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B10" s="20">
         <v>1</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D10" s="21">
         <v>8</v>
@@ -992,13 +996,13 @@
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B11" s="22">
         <v>1</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D11" s="21">
         <v>3</v>
@@ -1020,13 +1024,13 @@
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B12" s="22">
         <v>2</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="D12" s="21">
         <v>5</v>
@@ -1048,13 +1052,13 @@
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1">
       <c r="A13" s="23" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B13" s="23">
         <v>1</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D13" s="24">
         <v>5</v>
@@ -1076,13 +1080,13 @@
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1">
       <c r="A14" s="23" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B14" s="25">
         <v>1</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D14" s="24">
         <v>5</v>
@@ -1104,13 +1108,13 @@
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1">
       <c r="A15" s="23" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B15" s="25">
         <v>2</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D15" s="24">
         <v>3</v>
@@ -1132,13 +1136,13 @@
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1">
       <c r="A16" s="23" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B16" s="24">
         <v>2</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D16" s="24">
         <v>3</v>
@@ -1156,13 +1160,13 @@
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1">
       <c r="A17" s="23" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B17" s="24">
         <v>3</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D17" s="24">
         <v>2</v>
@@ -1180,13 +1184,13 @@
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="26" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B18" s="26">
         <v>1</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D18" s="27">
         <v>5</v>
@@ -1204,13 +1208,13 @@
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1">
       <c r="A19" s="26" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B19" s="28">
         <v>1</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D19" s="27">
         <v>5</v>
@@ -1228,13 +1232,13 @@
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="26" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B20" s="28">
         <v>1</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D20" s="27">
         <v>3</v>
@@ -1252,13 +1256,13 @@
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="26" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B21" s="28">
         <v>2</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D21" s="27">
         <v>3</v>
@@ -1276,13 +1280,13 @@
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="26" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B22" s="28">
         <v>2</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D22" s="27">
         <v>2</v>
@@ -1300,13 +1304,13 @@
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B23" s="27">
         <v>3</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D23" s="27">
         <v>2</v>
@@ -1324,13 +1328,13 @@
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B24" s="28">
         <v>3</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D24" s="27">
         <v>2</v>
@@ -1348,13 +1352,13 @@
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B25" s="28">
         <v>4</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D25" s="27">
         <v>1</v>

--- a/JsonConverter/ExcelFiles/Wave.xlsx
+++ b/JsonConverter/ExcelFiles/Wave.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GameProjects\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0A9A76-F9E1-4A0A-8194-E04AB48B5753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A4F587-8F99-418B-9921-2E3B8244A894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="2700" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2490" yWindow="840" windowWidth="16470" windowHeight="14115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
     </ext>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="53">
   <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -87,112 +90,148 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Enemy_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy_04</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemy_05</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave1_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave1_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave1_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave2_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave2_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave2_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave3_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave3_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave3_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave4_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave4_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave4_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave4_04</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave4_05</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave5_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave5_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave5_03</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave5_04</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave5_05</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave5_06</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave5_07</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave5_08</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>Enemy_Normal</t>
+  </si>
+  <si>
+    <t>Wave1_01_02</t>
+  </si>
+  <si>
+    <t>Wave1_02_02</t>
+  </si>
+  <si>
+    <t>Wave1_03_01</t>
+  </si>
+  <si>
+    <t>Wave1_03_02</t>
+  </si>
+  <si>
+    <t>Wave1_03_03</t>
+  </si>
+  <si>
+    <t>Enemy_Cup</t>
+  </si>
+  <si>
+    <t>Enemy_Cup</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave1_02_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave1_01_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_Crazy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_02_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_02_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_02_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_02_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_Pharmacist</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_01_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_01_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_01_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_01_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_03_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_03_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_03_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave2_03_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_01_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_01_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_01_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_01_04</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_01_05</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_01_06</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_Special</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_02_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_02_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_02_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_03_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_03_02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave3_03_03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy_Crazy</t>
   </si>
 </sst>
 </file>
@@ -249,7 +288,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,12 +309,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFD86DCD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
@@ -284,24 +317,6 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-4.9989318521683403E-2"/>
-        <bgColor rgb="FF4D93D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-4.9989318521683403E-2"/>
-        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -358,24 +373,6 @@
         <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor rgb="FF4D93D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -419,39 +416,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -472,25 +463,7 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -711,12 +684,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N1000"/>
+  <dimension ref="A1:N1001"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" style="2" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="40" style="2" bestFit="1" customWidth="1"/>
@@ -747,8 +720,8 @@
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="7"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="5"/>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" s="1" t="s">
@@ -772,717 +745,848 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:14" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="8" t="s">
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" s="8" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="9"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A4" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="14">
-        <v>3</v>
-      </c>
-      <c r="E4" s="15">
+      <c r="D4" s="12">
+        <v>5</v>
+      </c>
+      <c r="E4" s="20">
         <v>1</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="12">
         <v>0</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A5" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="16">
+      <c r="A5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="13">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="14">
-        <v>3</v>
-      </c>
-      <c r="E5" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="14">
+      <c r="C5" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="12">
+        <v>5</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="12">
         <v>5</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A6" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="16">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14" t="s">
+      <c r="A6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="13">
+        <v>2</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="14">
-        <v>2</v>
-      </c>
-      <c r="E6" s="14">
-        <v>1.5</v>
-      </c>
-      <c r="F6" s="14">
-        <v>8</v>
+      <c r="D6" s="12">
+        <v>10</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="12">
+        <v>5</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="17">
-        <v>1</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="18">
+      <c r="A7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="13">
+        <v>2</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="12">
         <v>5</v>
       </c>
-      <c r="E7" s="18">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="18">
-        <v>0</v>
+      <c r="E7" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="12">
+        <v>8</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A8" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="19">
-        <v>1</v>
-      </c>
-      <c r="C8" s="18" t="s">
+      <c r="A8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="11">
+        <v>3</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="12">
+        <v>10</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="12">
         <v>5</v>
-      </c>
-      <c r="E8" s="18">
-        <v>0.25</v>
-      </c>
-      <c r="F8" s="18">
-        <v>3</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="13">
+        <v>3</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="19">
-        <v>1</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="18">
+      <c r="D9" s="12">
+        <v>2</v>
+      </c>
+      <c r="E9" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="12">
         <v>3</v>
-      </c>
-      <c r="E9" s="18">
-        <v>0.25</v>
-      </c>
-      <c r="F9" s="18">
-        <v>6</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A10" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="20">
-        <v>1</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="21">
-        <v>8</v>
-      </c>
-      <c r="E10" s="21">
-        <v>0.25</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0</v>
+      <c r="A10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="13">
+        <v>3</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="12">
+        <v>3</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="12">
+        <v>6</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A11" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="A11" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="14">
         <v>1</v>
       </c>
-      <c r="C11" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="21">
-        <v>3</v>
-      </c>
-      <c r="E11" s="21">
-        <v>0.25</v>
-      </c>
-      <c r="F11" s="21">
-        <v>6</v>
+      <c r="C11" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="15">
+        <v>1</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="15">
+        <v>0</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A12" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="22">
-        <v>2</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="21">
+      <c r="A12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="16">
+        <v>1</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="15">
         <v>5</v>
       </c>
-      <c r="E12" s="21">
-        <v>0.25</v>
-      </c>
-      <c r="F12" s="21">
+      <c r="E12" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="15">
         <v>6</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A13" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="23">
+      <c r="A13" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="16">
         <v>1</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="24">
-        <v>5</v>
-      </c>
-      <c r="E13" s="24">
-        <v>0.25</v>
-      </c>
-      <c r="F13" s="24">
-        <v>0</v>
+      <c r="C13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="15">
+        <v>1</v>
+      </c>
+      <c r="E13" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="15">
+        <v>6</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A14" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="25">
+      <c r="A14" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="16">
         <v>1</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="15">
         <v>5</v>
       </c>
-      <c r="E14" s="24">
-        <v>0.25</v>
-      </c>
-      <c r="F14" s="24">
-        <v>2</v>
+      <c r="E14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="15">
+        <v>6</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A15" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="25">
+      <c r="A15" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="14">
         <v>2</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="24">
-        <v>3</v>
-      </c>
-      <c r="E15" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="F15" s="24">
+      <c r="C15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="15">
+        <v>0</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A16" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="24">
+      <c r="A16" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="14">
         <v>2</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="24">
-        <v>3</v>
-      </c>
-      <c r="E16" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="F16" s="24">
-        <v>4</v>
+      <c r="C16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="15">
+        <v>5</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="15">
+        <v>6</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="7"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A17" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="24">
-        <v>3</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="24">
+      <c r="A17" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="14">
         <v>2</v>
       </c>
-      <c r="E17" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="F17" s="24">
-        <v>10</v>
+      <c r="C17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="15">
+        <v>6</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="7"/>
+      <c r="J17" s="5"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A18" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="26">
-        <v>1</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="27">
+      <c r="A18" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="14">
+        <v>2</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="15">
         <v>5</v>
       </c>
-      <c r="E18" s="27">
-        <v>0.25</v>
-      </c>
-      <c r="F18" s="27">
-        <v>0</v>
+      <c r="E18" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="15">
+        <v>6</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="7"/>
+      <c r="J18" s="5"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="14">
+        <v>3</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="15">
         <v>1</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="27">
-        <v>5</v>
-      </c>
-      <c r="E19" s="27">
-        <v>0.25</v>
-      </c>
-      <c r="F19" s="27">
-        <v>2</v>
+      <c r="E19" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="15">
+        <v>0</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="7"/>
+      <c r="J19" s="5"/>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="28">
-        <v>1</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="27">
+      <c r="B20" s="14">
         <v>3</v>
       </c>
-      <c r="E20" s="27">
-        <v>0.25</v>
-      </c>
-      <c r="F20" s="27">
-        <v>4</v>
+      <c r="C20" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="15">
+        <v>5</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="15">
+        <v>6</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="7"/>
+      <c r="J20" s="5"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="28">
-        <v>2</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="27">
+      <c r="B21" s="14">
         <v>3</v>
       </c>
-      <c r="E21" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="F21" s="27">
-        <v>4</v>
+      <c r="C21" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="15">
+        <v>1</v>
+      </c>
+      <c r="E21" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="15">
+        <v>6</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="7"/>
+      <c r="J21" s="5"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="28">
-        <v>2</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="27">
-        <v>2</v>
-      </c>
-      <c r="E22" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="F22" s="27">
+      <c r="B22" s="14">
+        <v>3</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="15">
+        <v>5</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="15">
         <v>6</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="7"/>
+      <c r="J22" s="5"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="27">
-        <v>3</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="27">
-        <v>2</v>
-      </c>
-      <c r="E23" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="F23" s="27">
-        <v>8</v>
+      <c r="B23" s="17">
+        <v>1</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="18">
+        <v>1</v>
+      </c>
+      <c r="E23" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="18">
+        <v>0</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="7"/>
+      <c r="J23" s="5"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="19">
+        <v>1</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="18">
         <v>3</v>
       </c>
-      <c r="C24" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="27">
+      <c r="E24" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F24" s="18">
         <v>2</v>
-      </c>
-      <c r="E24" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="F24" s="27">
-        <v>9</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="7"/>
+      <c r="J24" s="5"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="28">
-        <v>4</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="27">
+      <c r="B25" s="19">
         <v>1</v>
       </c>
-      <c r="E25" s="27">
-        <v>0</v>
-      </c>
-      <c r="F25" s="27">
-        <v>10</v>
+      <c r="C25" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="18">
+        <v>2</v>
+      </c>
+      <c r="E25" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F25" s="18">
+        <v>5</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="7"/>
+      <c r="J25" s="5"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="A26" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="19">
+        <v>1</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="18">
+        <v>1</v>
+      </c>
+      <c r="E26" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F26" s="18">
+        <v>8</v>
+      </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="7"/>
+      <c r="J26" s="5"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+      <c r="A27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="19">
+        <v>1</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="18">
+        <v>3</v>
+      </c>
+      <c r="E27" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F27" s="18">
+        <v>2</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="7"/>
+      <c r="J27" s="5"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="A28" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="19">
+        <v>1</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="18">
+        <v>2</v>
+      </c>
+      <c r="E28" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F28" s="18">
+        <v>5</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="7"/>
+      <c r="J28" s="5"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+      <c r="A29" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="17">
+        <v>2</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="18">
+        <v>5</v>
+      </c>
+      <c r="E29" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F29" s="18">
+        <v>10</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="7"/>
+      <c r="J29" s="5"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="A30" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="17">
+        <v>2</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="18">
+        <v>10</v>
+      </c>
+      <c r="E30" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F30" s="18">
+        <v>6</v>
+      </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="7"/>
+      <c r="J30" s="5"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="A31" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="17">
+        <v>2</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="18">
+        <v>5</v>
+      </c>
+      <c r="E31" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="18">
+        <v>6</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="7"/>
+      <c r="J31" s="5"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
+      <c r="A32" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="17">
+        <v>3</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="18">
+        <v>7</v>
+      </c>
+      <c r="E32" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="18">
+        <v>0</v>
+      </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="7"/>
-    </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-    </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-    </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-    </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:2" ht="15.75" customHeight="1"/>
+      <c r="J32" s="5"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A33" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="17">
+        <v>3</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="18">
+        <v>10</v>
+      </c>
+      <c r="E33" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F33" s="18">
+        <v>6</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="5"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A34" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="17">
+        <v>3</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="18">
+        <v>10</v>
+      </c>
+      <c r="E34" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F34" s="18">
+        <v>6</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="5"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:10" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2435,6 +2539,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
